--- a/hardware/amr_pin_mapping_template.xlsx
+++ b/hardware/amr_pin_mapping_template.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="331">
   <si>
     <t>Module Type</t>
   </si>
@@ -208,6 +208,44 @@
   </si>
   <si>
     <t>PG0</t>
+  </si>
+  <si>
+    <r>
+      <t>Ultrasonic 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>右边</t>
+    </r>
+  </si>
+  <si>
+    <t>PC7</t>
+  </si>
+  <si>
+    <t>PC5</t>
+  </si>
+  <si>
+    <r>
+      <t>Ultrasonic 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>左边</t>
+    </r>
+  </si>
+  <si>
+    <t>PA6</t>
+  </si>
+  <si>
+    <t>PA3</t>
   </si>
   <si>
     <t>Board Pin Number</t>
@@ -1015,7 +1053,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1178,6 +1216,11 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1649,10 +1692,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2186,7 +2230,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="3" width="16" customWidth="1"/>
@@ -2957,6 +3001,146 @@
       </c>
       <c r="H24">
         <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" s="2">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="2">
+        <v>32</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H27" s="2">
+        <v>28</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" s="2">
+        <v>25</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2978,54 +3162,54 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>14</v>
@@ -3033,43 +3217,43 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>14</v>
@@ -3077,10 +3261,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>14</v>
@@ -3088,7 +3272,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>46</v>
@@ -3099,7 +3283,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>47</v>
@@ -3110,32 +3294,32 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>14</v>
@@ -3143,142 +3327,142 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>14</v>
@@ -3286,10 +3470,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>14</v>
@@ -3297,10 +3481,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>14</v>
@@ -3308,18 +3492,18 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>46</v>
@@ -3330,7 +3514,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>47</v>
@@ -3341,164 +3525,164 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>14</v>
@@ -3506,10 +3690,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>14</v>
@@ -3517,10 +3701,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>14</v>
@@ -3528,128 +3712,128 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>46</v>
@@ -3660,7 +3844,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="2" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>47</v>
@@ -3671,32 +3855,32 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>14</v>
@@ -3704,10 +3888,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="2" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>14</v>
@@ -3715,10 +3899,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>14</v>
@@ -3726,10 +3910,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>14</v>
@@ -3737,10 +3921,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>14</v>
@@ -3748,109 +3932,109 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="2" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="2" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="2" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="2" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>14</v>
@@ -3858,7 +4042,7 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>46</v>
@@ -3869,7 +4053,7 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>47</v>
@@ -3880,194 +4064,194 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="2" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="2" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="2" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>47</v>
@@ -4078,10 +4262,10 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="2" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>46</v>

--- a/hardware/amr_pin_mapping_template.xlsx
+++ b/hardware/amr_pin_mapping_template.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="333">
   <si>
     <t>Module Type</t>
   </si>
@@ -135,15 +135,12 @@
     <t>S0</t>
   </si>
   <si>
-    <t>PL5</t>
+    <t>PG0</t>
   </si>
   <si>
     <t>S1</t>
   </si>
   <si>
-    <t>PL4</t>
-  </si>
-  <si>
     <t>S2</t>
   </si>
   <si>
@@ -207,10 +204,12 @@
     <t>Botton</t>
   </si>
   <si>
-    <t>PG0</t>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>Ultrasonic 3</t>
     </r>
     <r>
@@ -230,6 +229,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>Ultrasonic 4</t>
     </r>
     <r>
@@ -246,6 +250,18 @@
   </si>
   <si>
     <t>PA3</t>
+  </si>
+  <si>
+    <t>机械臂上下</t>
+  </si>
+  <si>
+    <t>PL4</t>
+  </si>
+  <si>
+    <t>机械臂夹子</t>
+  </si>
+  <si>
+    <t>PL5</t>
   </si>
   <si>
     <t>Board Pin Number</t>
@@ -1064,6 +1080,11 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1216,11 +1237,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1547,156 +1563,157 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2230,7 +2247,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="3" width="16" customWidth="1"/>
@@ -2546,7 +2563,7 @@
         <v>17</v>
       </c>
       <c r="H9" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>14</v>
@@ -2571,18 +2588,14 @@
       <c r="D10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="2">
-        <v>45</v>
-      </c>
+      <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
         <v>14</v>
       </c>
@@ -2601,13 +2614,13 @@
         <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>16</v>
@@ -2636,13 +2649,13 @@
         <v>31</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>16</v>
@@ -2671,11 +2684,11 @@
         <v>31</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>16</v>
@@ -2692,13 +2705,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -2727,13 +2740,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>14</v>
@@ -2742,7 +2755,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>28</v>
@@ -2762,10 +2775,10 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>26</v>
@@ -2797,10 +2810,10 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>29</v>
@@ -2832,13 +2845,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
@@ -2850,7 +2863,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>14</v>
@@ -2867,25 +2880,25 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>14</v>
@@ -2902,13 +2915,13 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>14</v>
@@ -2920,7 +2933,7 @@
         <v>16</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>14</v>
@@ -2937,13 +2950,13 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="C21" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -2955,7 +2968,7 @@
         <v>16</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>14</v>
@@ -2972,32 +2985,32 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" t="s">
         <v>53</v>
       </c>
-      <c r="C22" t="s">
+      <c r="H22" t="s">
         <v>54</v>
-      </c>
-      <c r="H22" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" t="s">
         <v>56</v>
-      </c>
-      <c r="H23" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E24" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="H24">
         <v>33</v>
@@ -3005,7 +3018,7 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -3017,7 +3030,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>16</v>
@@ -3040,7 +3053,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -3052,7 +3065,7 @@
         <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>16</v>
@@ -3075,7 +3088,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
@@ -3087,7 +3100,7 @@
         <v>14</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>16</v>
@@ -3110,7 +3123,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
@@ -3122,7 +3135,7 @@
         <v>14</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>16</v>
@@ -3141,6 +3154,28 @@
       </c>
       <c r="K28" s="2" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" t="s">
+        <v>65</v>
+      </c>
+      <c r="H29">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" t="s">
+        <v>67</v>
+      </c>
+      <c r="H30">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -3162,54 +3197,54 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>14</v>
@@ -3217,43 +3252,43 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>14</v>
@@ -3261,10 +3296,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>14</v>
@@ -3272,54 +3307,54 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>14</v>
@@ -3327,142 +3362,142 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>14</v>
@@ -3470,10 +3505,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>14</v>
@@ -3481,10 +3516,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>14</v>
@@ -3492,197 +3527,197 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>14</v>
@@ -3690,10 +3725,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>14</v>
@@ -3701,10 +3736,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>14</v>
@@ -3712,175 +3747,175 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>14</v>
@@ -3888,10 +3923,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>14</v>
@@ -3899,10 +3934,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>14</v>
@@ -3910,10 +3945,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>14</v>
@@ -3921,10 +3956,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>14</v>
@@ -3932,109 +3967,109 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>14</v>
@@ -4042,233 +4077,233 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/hardware/amr_pin_mapping_template.xlsx
+++ b/hardware/amr_pin_mapping_template.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="341">
   <si>
     <t>Module Type</t>
   </si>
@@ -262,6 +262,30 @@
   </si>
   <si>
     <t>PL5</t>
+  </si>
+  <si>
+    <t>RFID</t>
+  </si>
+  <si>
+    <t>PB0</t>
+  </si>
+  <si>
+    <t>SCK</t>
+  </si>
+  <si>
+    <t>PB1</t>
+  </si>
+  <si>
+    <t>MOSI</t>
+  </si>
+  <si>
+    <t>PB2</t>
+  </si>
+  <si>
+    <t>MISO</t>
+  </si>
+  <si>
+    <t>PB3</t>
   </si>
   <si>
     <t>Board Pin Number</t>
@@ -2247,7 +2271,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="3" width="16" customWidth="1"/>
@@ -3176,6 +3200,62 @@
       </c>
       <c r="H30">
         <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" t="s">
+        <v>69</v>
+      </c>
+      <c r="H31">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+      <c r="E32" t="s">
+        <v>71</v>
+      </c>
+      <c r="H32">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" t="s">
+        <v>72</v>
+      </c>
+      <c r="E33" t="s">
+        <v>73</v>
+      </c>
+      <c r="H33">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" t="s">
+        <v>75</v>
+      </c>
+      <c r="H34">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3197,54 +3277,54 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>14</v>
@@ -3252,43 +3332,43 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>14</v>
@@ -3296,10 +3376,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>14</v>
@@ -3307,7 +3387,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>45</v>
@@ -3318,7 +3398,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>46</v>
@@ -3329,32 +3409,32 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>14</v>
@@ -3362,142 +3442,142 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>14</v>
@@ -3505,10 +3585,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>14</v>
@@ -3516,10 +3596,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>14</v>
@@ -3527,18 +3607,18 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>45</v>
@@ -3549,7 +3629,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>46</v>
@@ -3560,164 +3640,164 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>14</v>
@@ -3725,10 +3805,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>14</v>
@@ -3736,10 +3816,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>14</v>
@@ -3747,128 +3827,128 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="2" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="2" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="2" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="2" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="2" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>45</v>
@@ -3879,7 +3959,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>46</v>
@@ -3890,32 +3970,32 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>14</v>
@@ -3923,10 +4003,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>14</v>
@@ -3934,10 +4014,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="2" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>14</v>
@@ -3945,10 +4025,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="2" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>14</v>
@@ -3956,10 +4036,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>14</v>
@@ -3967,109 +4047,109 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="2" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="2" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="2" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="2" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="2" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="2" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="2" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>14</v>
@@ -4077,7 +4157,7 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="2" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>45</v>
@@ -4088,7 +4168,7 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="2" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>46</v>
@@ -4099,194 +4179,194 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="2" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="2" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="2" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="2" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="2" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="2" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="2" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="2" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="2" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="2" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="2" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="2" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="2" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="2" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="2" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="2" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="2" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="2" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>46</v>
@@ -4297,10 +4377,10 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="2" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>45</v>

--- a/hardware/amr_pin_mapping_template.xlsx
+++ b/hardware/amr_pin_mapping_template.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\李仁杰\香港大学\2025-2026\ELEC3848\Group project\hardware\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BCDF08-6B3A-4B37-B4D9-DEFE6DA7DC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pin Mapping" sheetId="1" r:id="rId1"/>
@@ -28,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="342">
   <si>
     <t>Module Type</t>
   </si>
@@ -129,9 +135,6 @@
     <t>OUT</t>
   </si>
   <si>
-    <t>PL3</t>
-  </si>
-  <si>
     <t>S0</t>
   </si>
   <si>
@@ -144,19 +147,10 @@
     <t>S2</t>
   </si>
   <si>
-    <t>PB7</t>
-  </si>
-  <si>
     <t>S3</t>
   </si>
   <si>
-    <t>PB5</t>
-  </si>
-  <si>
     <t>LED</t>
-  </si>
-  <si>
-    <t>PL2</t>
   </si>
   <si>
     <t>OLED</t>
@@ -208,7 +202,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>Ultrasonic 3</t>
     </r>
@@ -232,7 +226,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>Ultrasonic 4</t>
     </r>
@@ -1082,18 +1076,54 @@
   <si>
     <t>AVCC</t>
   </si>
+  <si>
+    <r>
+      <t>LED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>红色</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IN</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PG0</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>LED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>绿色</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PL2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1104,7 +1134,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1113,157 +1143,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1276,194 +1171,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1486,342 +1195,169 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1832,7 +1368,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1860,154 +1396,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2265,14 +1687,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K36"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
@@ -2284,7 +1706,7 @@
     <col min="11" max="11" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:11">
+    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2319,7 +1741,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -2354,7 +1776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2389,7 +1811,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -2424,7 +1846,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -2459,7 +1881,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
@@ -2494,7 +1916,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -2529,7 +1951,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>30</v>
       </c>
@@ -2542,18 +1964,14 @@
       <c r="D8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="2">
-        <v>46</v>
-      </c>
+      <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
         <v>14</v>
       </c>
@@ -2564,7 +1982,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>30</v>
       </c>
@@ -2572,23 +1990,19 @@
         <v>31</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="2">
-        <v>41</v>
-      </c>
+      <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
         <v>14</v>
       </c>
@@ -2599,7 +2013,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
@@ -2607,7 +2021,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -2630,7 +2044,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
@@ -2638,23 +2052,19 @@
         <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="2">
-        <v>13</v>
-      </c>
+      <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
         <v>14</v>
       </c>
@@ -2665,7 +2075,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>30</v>
       </c>
@@ -2673,23 +2083,19 @@
         <v>31</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="2">
-        <v>11</v>
-      </c>
+      <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
         <v>14</v>
       </c>
@@ -2700,7 +2106,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
@@ -2708,34 +2114,30 @@
         <v>31</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="2">
-        <v>47</v>
-      </c>
+      <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -2762,15 +2164,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>14</v>
@@ -2779,7 +2181,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>28</v>
@@ -2797,12 +2199,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>26</v>
@@ -2832,12 +2234,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>29</v>
@@ -2867,15 +2269,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
@@ -2887,7 +2289,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>14</v>
@@ -2902,15 +2304,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>14</v>
@@ -2919,10 +2321,10 @@
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>14</v>
@@ -2937,15 +2339,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>14</v>
@@ -2957,7 +2359,7 @@
         <v>16</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>14</v>
@@ -2972,15 +2374,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -2992,7 +2394,7 @@
         <v>16</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>14</v>
@@ -3007,42 +2409,42 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="H23" t="s">
         <v>52</v>
       </c>
-      <c r="C22" t="s">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>53</v>
       </c>
-      <c r="H22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" t="s">
-        <v>55</v>
-      </c>
-      <c r="H23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" t="s">
-        <v>57</v>
-      </c>
       <c r="E24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H24">
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="3" t="s">
-        <v>58</v>
+    <row r="25" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -3054,7 +2456,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>16</v>
@@ -3075,9 +2477,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="3" t="s">
-        <v>58</v>
+    <row r="26" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -3089,7 +2491,7 @@
         <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>16</v>
@@ -3110,9 +2512,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="3" t="s">
-        <v>61</v>
+    <row r="27" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
@@ -3124,7 +2526,7 @@
         <v>14</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>16</v>
@@ -3145,9 +2547,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="3" t="s">
-        <v>61</v>
+    <row r="28" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
@@ -3159,7 +2561,7 @@
         <v>14</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>16</v>
@@ -3180,1214 +2582,1241 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="4" t="s">
-        <v>64</v>
+    <row r="29" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="E29" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H29">
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="4" t="s">
-        <v>66</v>
+    <row r="30" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E30" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H30">
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C31" t="s">
         <v>29</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H31">
         <v>53</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E32" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H32">
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" t="s">
         <v>68</v>
       </c>
-      <c r="C33" t="s">
-        <v>72</v>
-      </c>
       <c r="E33" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H33">
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E34" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H34">
         <v>50</v>
       </c>
     </row>
+    <row r="35" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="H35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="H36">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C101"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:3">
+    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="2" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="2" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
+      <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="2" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C15" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B15" s="2" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="2" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C17" s="2" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="2" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C19" s="2" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="2" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C21" s="2" t="s">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C22" s="2" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
+      <c r="B24" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C23" s="2" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C24" s="2" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C25" s="2" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C26" s="2" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="2" t="s">
+      <c r="B28" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C28" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="2" t="s">
+      <c r="C29" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="2" t="s">
+      <c r="C30" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="2" t="s">
+      <c r="C31" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="2" t="s">
+      <c r="B33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B34" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="2" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="2" t="s">
+      <c r="C35" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B35" s="2" t="s">
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="2" t="s">
+      <c r="B37" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C36" s="2" t="s">
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="2" t="s">
+      <c r="B38" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C37" s="2" t="s">
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="2" t="s">
+      <c r="B39" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C38" s="2" t="s">
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="2" t="s">
+      <c r="B40" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C39" s="2" t="s">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="2" t="s">
+      <c r="B41" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C40" s="2" t="s">
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="2" t="s">
+      <c r="B42" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="2" t="s">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="2" t="s">
+      <c r="B43" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C42" s="2" t="s">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="2" t="s">
+      <c r="B44" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C43" s="2" t="s">
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="2" t="s">
+      <c r="B45" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C44" s="2" t="s">
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="2" t="s">
+      <c r="B46" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C46" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C45" s="2" t="s">
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C46" s="2" t="s">
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="2" t="s">
+      <c r="B48" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C48" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="B49" s="2" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="2" t="s">
+      <c r="C49" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B50" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="2" t="s">
+      <c r="C50" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B51" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B50" s="2" t="s">
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="2" t="s">
+      <c r="B52" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="2" t="s">
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="2" t="s">
+      <c r="B53" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C52" s="2" t="s">
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="2" t="s">
+      <c r="B54" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C53" s="2" t="s">
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C54" s="2" t="s">
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="2" t="s">
+      <c r="B56" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C55" s="2" t="s">
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="2" t="s">
+      <c r="B57" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C56" s="2" t="s">
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="2" t="s">
+      <c r="B58" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C57" s="2" t="s">
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="2" t="s">
+      <c r="B59" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C58" s="2" t="s">
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="2" t="s">
+      <c r="B60" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C59" s="2" t="s">
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="2" t="s">
+      <c r="B61" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C60" s="2" t="s">
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="2" t="s">
+      <c r="B62" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B63" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="B64" s="2" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="2" t="s">
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="2" t="s">
+      <c r="B65" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C64" s="2" t="s">
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="2" t="s">
+      <c r="B66" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C66" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="B67" s="2" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="2" t="s">
+      <c r="C67" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B68" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="2" t="s">
+      <c r="C68" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B69" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="2" t="s">
+      <c r="C69" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B70" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="2" t="s">
+      <c r="C70" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B71" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="2" t="s">
+      <c r="C71" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B70" s="2" t="s">
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="2" t="s">
+      <c r="B72" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C71" s="2" t="s">
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="2" t="s">
+      <c r="B73" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C72" s="2" t="s">
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="2" t="s">
+      <c r="B74" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C73" s="2" t="s">
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="2" t="s">
+      <c r="B75" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C74" s="2" t="s">
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="2" t="s">
+      <c r="B76" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="C76" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C75" s="2" t="s">
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="2" t="s">
+      <c r="B77" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="C77" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C76" s="2" t="s">
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="2" t="s">
+      <c r="B78" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="C78" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C77" s="2" t="s">
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="2" t="s">
+      <c r="B79" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C78" s="2" t="s">
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="2" t="s">
+      <c r="B80" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="C80" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="B81" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="2" t="s">
+      <c r="B82" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B83" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="2" t="s">
+      <c r="C83" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="2" t="s">
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="2" t="s">
+      <c r="B84" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="C84" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C83" s="2" t="s">
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="2" t="s">
+      <c r="B85" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="C85" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C84" s="2" t="s">
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="2" t="s">
+      <c r="B86" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="C86" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C85" s="2" t="s">
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="2" t="s">
+      <c r="B87" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="C87" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C86" s="2" t="s">
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="2" t="s">
+      <c r="B88" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C87" s="2" t="s">
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="2" t="s">
+      <c r="B89" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="C89" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C88" s="2" t="s">
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="2" t="s">
+      <c r="B90" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="C90" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C89" s="2" t="s">
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="2" t="s">
+      <c r="B91" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="C91" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C90" s="2" t="s">
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="2" t="s">
+      <c r="B92" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="C92" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C91" s="2" t="s">
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="2" t="s">
+      <c r="B93" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="C93" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C92" s="2" t="s">
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="2" t="s">
+      <c r="B94" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="C94" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="C93" s="2" t="s">
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="2" t="s">
+      <c r="B95" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="C95" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C94" s="2" t="s">
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="2" t="s">
+      <c r="B96" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="C96" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="C95" s="2" t="s">
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="2" t="s">
+      <c r="B97" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="C97" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C96" s="2" t="s">
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="2" t="s">
+      <c r="B98" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="C98" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="C97" s="2" t="s">
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="2" t="s">
+      <c r="B99" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="C99" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C98" s="2" t="s">
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="2" t="s">
+      <c r="B100" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B101" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>340</v>
-      </c>
       <c r="C101" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/hardware/amr_pin_mapping_template.xlsx
+++ b/hardware/amr_pin_mapping_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\李仁杰\香港大学\2025-2026\ELEC3848\Group project\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BCDF08-6B3A-4B37-B4D9-DEFE6DA7DC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A7350A-F1E3-45DD-BF02-5225CE250412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="344">
   <si>
     <t>Module Type</t>
   </si>
@@ -1116,6 +1116,14 @@
   </si>
   <si>
     <t>PL2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2450-450)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2592,6 +2600,9 @@
       <c r="H29">
         <v>45</v>
       </c>
+      <c r="K29" s="4" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="30" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
@@ -2602,6 +2613,9 @@
       </c>
       <c r="H30">
         <v>44</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">

--- a/hardware/amr_pin_mapping_template.xlsx
+++ b/hardware/amr_pin_mapping_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\李仁杰\香港大学\2025-2026\ELEC3848\Group project\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A7350A-F1E3-45DD-BF02-5225CE250412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD16EC4-7923-4D13-AB74-C3FA94560AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="346">
   <si>
     <t>Module Type</t>
   </si>
@@ -249,13 +249,7 @@
     <t>机械臂上下</t>
   </si>
   <si>
-    <t>PL4</t>
-  </si>
-  <si>
     <t>机械臂夹子</t>
-  </si>
-  <si>
-    <t>PL5</t>
   </si>
   <si>
     <t>RFID</t>
@@ -1124,6 +1118,22 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PL5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PL4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>门舵机</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PB7</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1207,12 +1217,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1701,7 +1712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="16" customWidth="1"/>
@@ -2594,39 +2605,39 @@
       <c r="A29" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E29" t="s">
-        <v>61</v>
+      <c r="E29" s="4" t="s">
+        <v>342</v>
       </c>
       <c r="H29">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E30" t="s">
-        <v>63</v>
+        <v>61</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>343</v>
       </c>
       <c r="H30">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C31" t="s">
         <v>29</v>
       </c>
       <c r="E31" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H31">
         <v>53</v>
@@ -2634,13 +2645,13 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" t="s">
         <v>64</v>
       </c>
-      <c r="C32" t="s">
-        <v>66</v>
-      </c>
       <c r="E32" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H32">
         <v>52</v>
@@ -2648,13 +2659,13 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C33" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E33" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H33">
         <v>51</v>
@@ -2662,13 +2673,13 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E34" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H34">
         <v>50</v>
@@ -2676,13 +2687,13 @@
     </row>
     <row r="35" spans="1:8" ht="15" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>339</v>
       </c>
       <c r="H35">
         <v>41</v>
@@ -2690,16 +2701,27 @@
     </row>
     <row r="36" spans="1:8" ht="15" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H36">
         <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A37" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="H37">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2720,54 +2742,54 @@
   <sheetData>
     <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>14</v>
@@ -2775,43 +2797,43 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>14</v>
@@ -2819,10 +2841,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>14</v>
@@ -2830,7 +2852,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>41</v>
@@ -2841,7 +2863,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>42</v>
@@ -2852,32 +2874,32 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>14</v>
@@ -2885,142 +2907,142 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>14</v>
@@ -3028,10 +3050,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>14</v>
@@ -3039,10 +3061,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>14</v>
@@ -3050,18 +3072,18 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>41</v>
@@ -3072,7 +3094,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>42</v>
@@ -3083,164 +3105,164 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>14</v>
@@ -3248,10 +3270,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>14</v>
@@ -3259,10 +3281,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>14</v>
@@ -3270,128 +3292,128 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>41</v>
@@ -3402,7 +3424,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>42</v>
@@ -3413,32 +3435,32 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>14</v>
@@ -3446,10 +3468,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>14</v>
@@ -3457,10 +3479,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>14</v>
@@ -3468,10 +3490,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>14</v>
@@ -3479,10 +3501,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>14</v>
@@ -3490,109 +3512,109 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>14</v>
@@ -3600,7 +3622,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>41</v>
@@ -3611,7 +3633,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>42</v>
@@ -3622,194 +3644,194 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>42</v>
@@ -3820,10 +3842,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>41</v>
